--- a/SAS/README_Overview of SAS Programs and Input Datasets for ASE 2.0.xlsx
+++ b/SAS/README_Overview of SAS Programs and Input Datasets for ASE 2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\CDC National Sepsis Surveillance - ASE variants\ASE algorithm\ASE 2.1_refresh\v6 FINAL ASE 2.0  (091125)\gitrepo_092425\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\CDC National Sepsis Surveillance - ASE variants\ASE algorithm\ASE 2.1_refresh\v6 FINAL ASE 2.0  (091125)\gitrepo_092425\new files for thurs 092525\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C766118-1961-42D3-ABCD-643E0FE3351D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9521520-AA80-4AA7-9E85-A11D49B4E1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="834" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Sheet" sheetId="14" r:id="rId1"/>
@@ -30,7 +30,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">basic!$A$1:$E$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover Sheet'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover Sheet'!$A$1:$C$21</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="298">
   <si>
     <t>Sequence</t>
   </si>
@@ -1213,10 +1213,6 @@
 9=ECMO  </t>
   </si>
   <si>
-    <t>v0 9/24/2025
-Christina Chan</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">derived.raw_meds
  ase_med_mappings_011525 </t>
@@ -1546,14 +1542,211 @@
 --&gt;  includes all episodes of ASE during hospital encounter, separated by  7 or 14 day intervals between events</t>
   </si>
   <si>
-    <t>Updated 9/24/25</t>
+    <t>Project File Structure / Folder Layout</t>
+  </si>
+  <si>
+    <t>Note: This information is also included in the script "0.0_user_inputs"</t>
+  </si>
+  <si>
+    <t>v1 9/25/2025
+Christina Chan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The project code anticipates the following files structure when running the analysis:
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Project Folder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g. "Adult Sepsis Event 2.0", specific name not necessary)
+       -Sub-Folder Name "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reorganize Data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+                               Includes 14 SAS programs in the Reorganize Data Folder
+                     -Secondary sub-folder name:  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Output</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+                               Includes all of the datasets output from the 14 SAS programs [these are copied to the "Raw Datasets" folder below]
+                     -Secondary sub-folder name:  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tmp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"  
+                               Includes all interim datasets produced by each SAS program
+      -Sub-Folder Name "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Run Analysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+                            Includes 3 SAS programs in the Run Analysis Folder
+                    -Secondary sub-folder name:  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raw Datasets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+                             Includes all of the input datasets created by the SAS programs in the Reorganize Data Folder (eg, basic, medications, laboratory, etc).  
+                             Alternatively, the filepath in your libname statement can direct  to "Reorganize-Data/Output" folder
+                    -Secondary sub-folder name:  "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Working Datasets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+                             Includes all of the final ASE datasets created by the SAS programs in the Reorganize Data Folder (ehr_infection,
+                             ehr_organ_dysfunction, ehr_sepsis_ase22)
+                    -Secondary sub-folder name:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Output Tables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+                             Includes results tables for final reporting</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1611,14 +1804,6 @@
     </font>
     <font>
       <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1723,7 +1908,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1769,6 +1954,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1936,7 +2127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2014,30 +2205,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -2047,7 +2235,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2056,68 +2244,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2137,13 +2343,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2158,13 +2364,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2182,10 +2388,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
     </xf>
   </cellXfs>
@@ -2471,7 +2677,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="6" customWidth="1"/>
@@ -2487,22 +2693,20 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="23"/>
-      <c r="B2" s="44">
-        <v>45924</v>
-      </c>
+      <c r="B2" s="43"/>
       <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>176</v>
       </c>
       <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
-      <c r="B4" s="42" t="s">
-        <v>293</v>
+      <c r="B4" s="41" t="s">
+        <v>292</v>
       </c>
       <c r="C4" s="23"/>
     </row>
@@ -2576,26 +2780,46 @@
       </c>
       <c r="C16" s="23"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
-      <c r="B17" s="31"/>
+      <c r="B17" s="69" t="s">
+        <v>294</v>
+      </c>
       <c r="C17" s="23"/>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="323.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
-      <c r="B18" s="41" t="s">
-        <v>249</v>
+      <c r="B18" s="67" t="s">
+        <v>297</v>
       </c>
       <c r="C18" s="23"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="68"/>
+    </row>
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
+      <c r="B19" s="67" t="s">
+        <v>295</v>
+      </c>
       <c r="C19" s="23"/>
+      <c r="D19" s="68"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23"/>
+      <c r="B20" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="68"/>
+    </row>
+    <row r="21" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="65" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="63" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2612,124 +2836,124 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>227</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="88"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="93"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="48" t="s">
+      <c r="C5" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="48"/>
+      <c r="C6" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="48" t="s">
+      <c r="C7" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="47" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="48" t="s">
+      <c r="C8" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="47" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="48" t="s">
+      <c r="C9" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="47" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="48" t="s">
+      <c r="C10" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="48" t="s">
+      <c r="C11" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="48" t="s">
+      <c r="C12" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="48" t="s">
+      <c r="C13" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="47" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2752,208 +2976,208 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="2:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
-        <v>292</v>
-      </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="B3" s="89" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="67" t="s">
+      <c r="C5" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="66" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="67"/>
+      <c r="D6" s="66"/>
     </row>
     <row r="7" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="67" t="s">
+      <c r="C7" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="66" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="67"/>
+      <c r="C8" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="66"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="67"/>
+      <c r="C9" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="66"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="67"/>
+      <c r="D10" s="66"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="67"/>
+      <c r="C11" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="66"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="67" t="s">
+      <c r="C12" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="66" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="67" t="s">
+      <c r="C13" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="66" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="67"/>
+      <c r="C14" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="66"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="67"/>
+      <c r="C15" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="66"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="67"/>
+      <c r="C16" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="66"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="67"/>
+      <c r="C17" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="66"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="67"/>
+      <c r="C18" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="66"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="67"/>
+      <c r="C19" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="66"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="67"/>
+      <c r="C20" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="66"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="67"/>
+      <c r="C21" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="66"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="67"/>
+      <c r="C22" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="66"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="67"/>
+      <c r="C23" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2977,116 +3201,116 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="65" t="s">
+      <c r="C5" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="64" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="65"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="65" t="s">
+      <c r="C7" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="64" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65"/>
+      <c r="C8" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="64"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="65"/>
+      <c r="C9" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="65" t="s">
+      <c r="C10" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="64" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="65"/>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="65"/>
+      <c r="D12" s="64"/>
     </row>
     <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="65" t="s">
+      <c r="C13" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="64" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3112,160 +3336,160 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="65" t="s">
+      <c r="C5" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="64" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="65"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="65" t="s">
+      <c r="C7" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="64" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65"/>
+      <c r="C8" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="64"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="65"/>
+      <c r="C9" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="65"/>
+      <c r="D10" s="64"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="65" t="s">
+      <c r="C12" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="64" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="65" t="s">
+      <c r="C13" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="64" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="65" t="s">
+      <c r="C14" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="64" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="65" t="s">
+      <c r="C15" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="64" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="94" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="90"/>
+      <c r="C17" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3288,27 +3512,27 @@
   <sheetData>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
       <c r="H4" t="s">
@@ -3316,190 +3540,190 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="64"/>
+      <c r="C5" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="63"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="64"/>
+      <c r="D6" s="63"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="64"/>
+      <c r="C7" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="63"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="64"/>
+      <c r="C8" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="63"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="64"/>
+      <c r="D9" s="63"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="64" t="s">
+      <c r="C10" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="64"/>
+      <c r="D10" s="63"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="64"/>
+      <c r="C11" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="63" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="64"/>
+      <c r="C12" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="63"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="64"/>
+      <c r="C13" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="63"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="64"/>
+      <c r="D14" s="63"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="64"/>
+      <c r="C15" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="63"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="C16" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="64"/>
+      <c r="C16" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="63"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="64" t="s">
+      <c r="B17" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="64"/>
+      <c r="C17" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="63"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="64" t="s">
+      <c r="C18" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="63" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="64"/>
+      <c r="C19" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="63"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="64"/>
+      <c r="C20" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="63"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="C21" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="64"/>
+      <c r="C21" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="63"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="64" t="s">
+      <c r="C22" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="63" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="64" t="s">
+      <c r="C23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="63" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="C24" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="64" t="s">
+      <c r="C24" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="63" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3517,7 +3741,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:O26"/>
+  <dimension ref="A2:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="6" customWidth="1"/>
@@ -3541,9 +3765,7 @@
       <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="45" t="s">
-        <v>295</v>
-      </c>
+      <c r="B3" s="44"/>
       <c r="C3" s="19"/>
       <c r="D3" s="12"/>
       <c r="E3" s="13"/>
@@ -3567,17 +3789,17 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="70"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="75"/>
     </row>
     <row r="6" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
-      <c r="B6" s="46">
+      <c r="B6" s="45">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -3592,17 +3814,17 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="73"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
     </row>
     <row r="8" spans="1:6" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
-      <c r="B8" s="46">
+      <c r="B8" s="45">
         <v>1</v>
       </c>
       <c r="C8" s="20" t="s">
@@ -3612,7 +3834,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>37</v>
@@ -3620,7 +3842,7 @@
     </row>
     <row r="9" spans="1:6" ht="210" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
-      <c r="B9" s="46">
+      <c r="B9" s="45">
         <v>2</v>
       </c>
       <c r="C9" s="20" t="s">
@@ -3638,14 +3860,14 @@
     </row>
     <row r="10" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
-      <c r="B10" s="46">
+      <c r="B10" s="45">
         <v>3</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>39</v>
@@ -3656,164 +3878,164 @@
     </row>
     <row r="11" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
-      <c r="B11" s="46">
+      <c r="B11" s="45">
         <v>4</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
-      <c r="B12" s="46">
+      <c r="B12" s="45">
         <v>5</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
-      <c r="B13" s="46">
+      <c r="B13" s="45">
         <v>6</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
-      <c r="B14" s="46">
+      <c r="B14" s="45">
         <v>7</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
-      <c r="B15" s="46">
+      <c r="B15" s="45">
         <v>8</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
-      <c r="B16" s="46">
+      <c r="B16" s="45">
         <v>9</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
-      <c r="B17" s="46">
+      <c r="B17" s="45">
         <v>10</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
-      <c r="B18" s="46">
+      <c r="B18" s="45">
         <v>11</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
-      <c r="B19" s="46">
+      <c r="B19" s="45">
         <v>12</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>2</v>
@@ -3821,70 +4043,70 @@
     </row>
     <row r="20" spans="1:15" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
-      <c r="B20" s="46">
+      <c r="B20" s="45">
         <v>13</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
-      <c r="B21" s="46">
+      <c r="B21" s="45">
         <v>14</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>283</v>
-      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="70"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="75"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="73"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="78"/>
     </row>
     <row r="24" spans="1:15" ht="60" x14ac:dyDescent="0.25">
-      <c r="B24" s="46">
+      <c r="B24" s="45">
         <v>15</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>33</v>
@@ -3894,7 +4116,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="46">
+      <c r="B25" s="45">
         <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -3904,14 +4126,14 @@
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>287</v>
-      </c>
     </row>
     <row r="26" spans="1:15" ht="111" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="46">
+      <c r="B26" s="45">
         <v>17</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -3921,14 +4143,22 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>294</v>
-      </c>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="70"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B22:F22"/>
@@ -3952,201 +4182,201 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
     </row>
     <row r="3" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="79"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="84"/>
     </row>
     <row r="4" spans="1:4" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="79" t="s">
         <v>240</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="76"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="81"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="46" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="48" t="s">
+      <c r="C6" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="48"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="48"/>
+      <c r="C8" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="48" t="s">
+      <c r="C9" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="47" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="48" t="s">
+      <c r="C10" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="48" t="s">
+      <c r="C11" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="48"/>
+      <c r="C12" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="48"/>
+      <c r="D13" s="47"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="48"/>
+      <c r="D14" s="47"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="48"/>
+      <c r="C15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="47"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="48"/>
+      <c r="D16" s="47"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="48"/>
+      <c r="D17" s="47"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="47" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="48"/>
+      <c r="D19" s="47"/>
       <c r="H19" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="48"/>
+      <c r="C20" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="47"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="48" t="s">
+      <c r="C21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="47" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="48" t="s">
+      <c r="C22" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="47" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4168,406 +4398,406 @@
   <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6" style="36" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="68" style="34" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="35" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" style="34" customWidth="1"/>
-    <col min="6" max="6" width="30.85546875" style="36" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="36"/>
+    <col min="1" max="1" width="6" style="35" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="68" style="33" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" style="34" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" style="35" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="32"/>
+      <c r="A1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:6" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="86" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
-    </row>
-    <row r="4" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36"/>
-      <c r="B4" s="49" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="88"/>
+    </row>
+    <row r="4" spans="1:6" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="35"/>
+      <c r="B4" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="49" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="49" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="38"/>
-      <c r="B5" s="51" t="s">
+      <c r="A5" s="37"/>
+      <c r="B5" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="51" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="51" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="51" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="52" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="51" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="51"/>
     </row>
     <row r="11" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="35" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="51"/>
     </row>
     <row r="13" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="54" t="s">
-        <v>289</v>
-      </c>
-      <c r="D13" s="53" t="s">
+      <c r="C13" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="D13" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="51" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="56"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="55"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="56"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="55"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="59"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58"/>
     </row>
     <row r="17" spans="2:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="59"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="59"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="58"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="59"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="58"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="60" t="s">
+      <c r="B20" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="58" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="59"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="58"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
     </row>
     <row r="23" spans="2:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E23" s="52" t="s">
+      <c r="E23" s="51" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="D24" s="53"/>
-      <c r="E24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="51"/>
     </row>
     <row r="25" spans="2:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="52" t="s">
+      <c r="E25" s="51" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="D26" s="53"/>
-      <c r="E26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="51"/>
     </row>
     <row r="27" spans="2:5" ht="102" x14ac:dyDescent="0.2">
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="51" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="38" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="51" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="D30" s="40"/>
-      <c r="E30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="38"/>
     </row>
     <row r="31" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="38"/>
     </row>
     <row r="32" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="38"/>
     </row>
     <row r="33" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="38"/>
     </row>
     <row r="34" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="40"/>
-      <c r="E34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B35" s="48" t="s">
+      <c r="B35" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="39"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4593,108 +4823,108 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="64" t="s">
+      <c r="C5" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="63" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="64"/>
+      <c r="D6" s="63"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="64"/>
+      <c r="D7" s="63"/>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65" t="s">
+      <c r="C8" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="64" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="64"/>
+      <c r="C9" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="63"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="64"/>
+      <c r="C10" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="63"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="64" t="s">
+      <c r="C11" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="63" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="64"/>
+      <c r="C12" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4718,127 +4948,127 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="65" t="s">
+      <c r="C5" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="64" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="65"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="65" t="s">
+      <c r="C7" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="64" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65"/>
+      <c r="C8" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="64"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="65"/>
+      <c r="C9" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="65"/>
+      <c r="C10" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="64"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="65" t="s">
+      <c r="C11" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="64" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="65" t="s">
+      <c r="C12" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="64" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="65"/>
+      <c r="C13" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="64"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="65"/>
+      <c r="C14" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4862,134 +5092,134 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="65" t="s">
+      <c r="C5" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="64" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="65"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="65"/>
+      <c r="C7" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="64"/>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65" t="s">
+      <c r="C8" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="64" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="65"/>
+      <c r="C9" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="65"/>
+      <c r="C10" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="64"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="65"/>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="65" t="s">
+      <c r="C12" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="64" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="65"/>
+      <c r="C13" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="64"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="65"/>
+      <c r="C14" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="64"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="65"/>
+      <c r="C15" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5013,173 +5243,173 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="89" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="67" t="s">
+      <c r="C5" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="66" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="67"/>
+      <c r="D6" s="66"/>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="67" t="s">
+      <c r="C7" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="66" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="67"/>
+      <c r="C8" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="66"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="67"/>
+      <c r="C9" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="66"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="67"/>
+      <c r="C10" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="66"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C11" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="67"/>
+      <c r="D11" s="66"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="67"/>
+      <c r="C12" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="66"/>
     </row>
     <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="67" t="s">
+      <c r="C13" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="66" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="67"/>
+      <c r="C14" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="66"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="67" t="s">
+      <c r="C15" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="66" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="67"/>
+      <c r="C16" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="66"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="67" t="s">
+      <c r="C17" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="67"/>
+      <c r="D17" s="66"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="67"/>
+      <c r="D18" s="66"/>
     </row>
     <row r="19" spans="2:4" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="67" t="s">
+      <c r="C19" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="48" t="s">
-        <v>290</v>
+      <c r="D19" s="47" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -5204,159 +5434,159 @@
       <c r="A1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="82" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
-        <v>291</v>
-      </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
+      <c r="B3" s="89" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="65" t="s">
+      <c r="C5" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="64" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="65"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="65" t="s">
+      <c r="C7" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="64" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65"/>
+      <c r="C8" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="64"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="65"/>
+      <c r="C9" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="64"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="65"/>
+      <c r="C10" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="64"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="65"/>
+      <c r="D12" s="64"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="65"/>
+      <c r="D13" s="64"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="65"/>
+      <c r="D14" s="64"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="65"/>
+      <c r="D15" s="64"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="65" t="s">
+      <c r="B16" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="65"/>
+      <c r="D16" s="64"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="65"/>
+      <c r="D17" s="64"/>
     </row>
     <row r="18" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="65" t="s">
+      <c r="C18" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="64" t="s">
         <v>172</v>
       </c>
     </row>
